--- a/output/2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx
@@ -464,7 +464,6 @@
           <t>TICA Climate Solutions Malaysia Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Nilai, Negeri Sembilan</t>
@@ -475,8 +474,6 @@
           <t>Produzione e vendita AHU, fan coils, chiller, package units (HVAC/ventilazione industriale)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Produttore con fabbrica/ufficio aperto a Nilai (Negeri Sembilan) per servire il Sud-Est asiatico; vende anche tramite rete commerciale/contractor-dealer, non solo diretto. Sito web ufficiale non confermato con certezza. Fonte: maukerja.my, careerconnect.mmu.edu.my, jobstreet.my</t>
@@ -484,7 +481,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -526,7 +523,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -563,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ragione sociale confermata via sito ufficiale (reg. 202001000892 / 1357211-X). Copertura Negeri Sembilan pubblicizzata tramite annunci dedicati (Mudah.my).</t>
+          <t>Ragione sociale confermata via sito ufficiale (reg. 202001000892 / 1357211-X). Copertura Negeri Sembilan pubblicizzata tramite annunci dedicati (Mudah.my). [DUPLICATO — vedi anche: 2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -610,7 +607,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -640,7 +637,6 @@
           <t>+603 6157 1177</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Filiale malese del gruppo multinazionale svedese Systemair; sede confermata a Sungai Buloh, Selangor (non Negeri Sembilan); nessuna copertura specifica per Negeri Sembilan confermata ma rilevante come distributore/produttore nazionale di settore.</t>
@@ -648,7 +644,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
